--- a/output/customers.xlsx
+++ b/output/customers.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEE75BE-DAAB-49A7-B5ED-FF537E9193B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D51A84-DCC1-420A-8889-B04397CC3AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="4">
   <si>
     <t>Company Name</t>
   </si>
@@ -26,25 +26,7 @@
     <t>CC Email</t>
   </si>
   <si>
-    <t>Khushi jain's</t>
-  </si>
-  <si>
     <t/>
-  </si>
-  <si>
-    <t>Preets' Store</t>
-  </si>
-  <si>
-    <t>Tecnoprism</t>
-  </si>
-  <si>
-    <t>Test Sync Company 1771937935657</t>
-  </si>
-  <si>
-    <t>khushijain11@gmail.com</t>
-  </si>
-  <si>
-    <t>khushi123@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -478,54 +460,34 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{BB8F6A35-4157-42C1-8336-E5CCD1977D57}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{83126327-654C-4A93-AFD9-A88AB3E800AA}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
